--- a/MSFT.xlsx
+++ b/MSFT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5D62B3-0883-42A8-BFB4-3C61EA60D1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6811E2BF-41D4-4D2B-9054-1B88FE7DA5C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{2536FD49-C228-45BB-BAA0-A0BFE1B4D82F}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{2536FD49-C228-45BB-BAA0-A0BFE1B4D82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -67,9 +67,6 @@
     <t>SEC</t>
   </si>
   <si>
-    <t>MSFT</t>
-  </si>
-  <si>
     <t>Main</t>
   </si>
   <si>
@@ -688,7 +685,10 @@
     <t>Cloud Growth</t>
   </si>
   <si>
-    <t>Q226</t>
+    <t>IR</t>
+  </si>
+  <si>
+    <t>Q326</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1327,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="3">
-        <v>432.32</v>
+        <v>405.1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -1335,7 +1335,7 @@
         <v>3</v>
       </c>
       <c r="H3" s="4">
-        <v>7425.6290760000002</v>
+        <v>7428.4347040000002</v>
       </c>
       <c r="I3" s="35" t="s">
         <v>216</v>
@@ -1350,19 +1350,19 @@
       </c>
       <c r="H4" s="4">
         <f>H3*H2</f>
-        <v>3210247.9621363198</v>
+        <v>3009258.8985904003</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+      <c r="B5" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="4">
-        <f>24296+65166</f>
-        <v>89462</v>
+        <f>32105+46167</f>
+        <v>78272</v>
       </c>
       <c r="I5" s="35" t="s">
         <v>216</v>
@@ -1373,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="4">
-        <f>4837+35425</f>
+        <f>31423+8839</f>
         <v>40262</v>
       </c>
       <c r="I6" s="35" t="s">
@@ -1382,77 +1382,77 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="H7" s="4">
         <f>H4-H5+H6</f>
-        <v>3161047.9621363198</v>
+        <v>2971248.8985904003</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B8" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="11" t="s">
         <v>132</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>133</v>
       </c>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B9" s="12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="13">
         <f>Model!Y13/Model!$Y$18</f>
         <v>0.43578299785412977</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E9" s="15"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B10" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C10" s="13">
         <f>Model!Y14/Model!$Y$18</f>
         <v>0.35681823744910696</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E10" s="17"/>
       <c r="G10" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B11" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11" s="13">
         <f>Model!Y15/Model!$Y$18</f>
         <v>0.20739876469676324</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E11" s="17"/>
       <c r="G11" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -1461,60 +1461,61 @@
       <c r="D12" s="19"/>
       <c r="E12" s="20"/>
       <c r="G12" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{DA6CDF4D-BB31-47EE-8095-D8F09F0AB7A2}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{A33EEB00-3A7F-49CA-BDF7-A6DF09715CB9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1532,85 +1533,85 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C2" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="K2" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="L2" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="M2" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="N2" s="5" t="s">
-        <v>116</v>
-      </c>
       <c r="O2" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="P2" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="P2" s="33" t="s">
+      <c r="Q2" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="Q2" s="33" t="s">
+      <c r="R2" s="33" t="s">
         <v>213</v>
-      </c>
-      <c r="R2" s="33" t="s">
-        <v>214</v>
       </c>
       <c r="S2" s="5"/>
       <c r="T2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="U2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="U2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="W2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="X2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Y2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Y2" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="Z2" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="7"/>
       <c r="B3" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C3" s="4">
         <v>18388</v>
@@ -1657,7 +1658,9 @@
       <c r="P3" s="4">
         <v>30865</v>
       </c>
-      <c r="Q3" s="4"/>
+      <c r="Q3" s="4">
+        <v>32592</v>
+      </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4">
@@ -1695,7 +1698,7 @@
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="7"/>
       <c r="B4" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C4" s="4">
         <v>11577</v>
@@ -1742,7 +1745,9 @@
       <c r="P4" s="4">
         <v>24524</v>
       </c>
-      <c r="Q4" s="4"/>
+      <c r="Q4" s="4">
+        <v>25593</v>
+      </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4">
@@ -1780,7 +1785,7 @@
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
       <c r="B5" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C5" s="4">
         <v>5313</v>
@@ -1827,7 +1832,9 @@
       <c r="P5" s="4">
         <v>5958</v>
       </c>
-      <c r="Q5" s="4"/>
+      <c r="Q5" s="4">
+        <v>5341</v>
+      </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4">
@@ -1865,7 +1872,7 @@
     <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
       <c r="B6" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C6" s="4">
         <v>3610</v>
@@ -1912,7 +1919,9 @@
       <c r="P6" s="4">
         <v>5082</v>
       </c>
-      <c r="Q6" s="4"/>
+      <c r="Q6" s="4">
+        <v>4832</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4">
@@ -1950,7 +1959,7 @@
     <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
       <c r="B7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C7" s="4">
         <v>3628</v>
@@ -1997,7 +2006,9 @@
       <c r="P7" s="4">
         <v>4479</v>
       </c>
-      <c r="Q7" s="4"/>
+      <c r="Q7" s="4">
+        <v>4041</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4">
@@ -2035,7 +2046,7 @@
     <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
       <c r="B8" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C8" s="4">
         <v>2913</v>
@@ -2082,7 +2093,9 @@
       <c r="P8" s="4">
         <v>3812</v>
       </c>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="4">
+        <v>3808</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4">
@@ -2120,7 +2133,7 @@
     <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="4">
         <v>1929</v>
@@ -2167,7 +2180,9 @@
       <c r="P9" s="4">
         <v>2305</v>
       </c>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="4">
+        <v>2297</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4">
@@ -2205,7 +2220,7 @@
     <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C10" s="4">
         <v>1260</v>
@@ -2252,7 +2267,9 @@
       <c r="P10" s="4">
         <v>2204</v>
       </c>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="4">
+        <v>2292</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4">
@@ -2290,7 +2307,7 @@
     <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="4">
         <v>1448</v>
@@ -2337,7 +2354,9 @@
       <c r="P11" s="4">
         <v>2038</v>
       </c>
-      <c r="Q11" s="4"/>
+      <c r="Q11" s="4">
+        <v>2087</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4">
@@ -2375,7 +2394,7 @@
     <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4">
         <v>56</v>
@@ -2422,7 +2441,9 @@
       <c r="P12" s="4">
         <v>6</v>
       </c>
-      <c r="Q12" s="4"/>
+      <c r="Q12" s="4">
+        <v>3</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4">
@@ -2460,7 +2481,7 @@
     <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
       <c r="B13" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="4">
         <v>16465</v>
@@ -2507,7 +2528,9 @@
       <c r="P13" s="4">
         <v>34116</v>
       </c>
-      <c r="Q13" s="4"/>
+      <c r="Q13" s="4">
+        <v>35013</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4"/>
       <c r="T13" s="4">
@@ -2545,7 +2568,7 @@
     <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
       <c r="B14" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C14" s="4">
         <v>20325</v>
@@ -2592,7 +2615,9 @@
       <c r="P14" s="4">
         <v>32907</v>
       </c>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="4">
+        <v>34681</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="4"/>
       <c r="T14" s="4">
@@ -2630,7 +2655,7 @@
     <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
       <c r="B15" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="4">
         <v>13332</v>
@@ -2677,7 +2702,9 @@
       <c r="P15" s="4">
         <v>14250</v>
       </c>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="4">
+        <v>13192</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4">
@@ -2714,7 +2741,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="4">
         <v>15741</v>
@@ -2761,7 +2788,9 @@
       <c r="P16" s="4">
         <v>16451</v>
       </c>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="4">
+        <v>15089</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4">
@@ -2798,7 +2827,7 @@
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="4">
         <v>34381</v>
@@ -2845,7 +2874,9 @@
       <c r="P17" s="4">
         <v>64822</v>
       </c>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="4">
+        <v>67797</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4">
@@ -2872,10 +2903,10 @@
     </row>
     <row r="18" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B18" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="22">
-        <f t="shared" ref="C18:P18" si="3">+C16+C17</f>
+        <f t="shared" ref="C18:Q18" si="3">+C16+C17</f>
         <v>50122</v>
       </c>
       <c r="D18" s="22">
@@ -2930,7 +2961,10 @@
         <f t="shared" si="3"/>
         <v>81273</v>
       </c>
-      <c r="Q18" s="22"/>
+      <c r="Q18" s="22">
+        <f t="shared" si="3"/>
+        <v>82886</v>
+      </c>
       <c r="R18" s="22"/>
       <c r="S18" s="4"/>
       <c r="T18" s="22">
@@ -2964,7 +2998,7 @@
     </row>
     <row r="19" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="4">
         <v>4302</v>
@@ -3011,7 +3045,9 @@
       <c r="P19" s="4">
         <v>3505</v>
       </c>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="4">
+        <v>2733</v>
+      </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4">
@@ -3038,7 +3074,7 @@
     </row>
     <row r="20" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="4">
         <v>11150</v>
@@ -3085,7 +3121,9 @@
       <c r="P20" s="4">
         <v>22473</v>
       </c>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="4">
+        <v>24095</v>
+      </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4">
@@ -3112,10 +3150,10 @@
     </row>
     <row r="21" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="4">
-        <f t="shared" ref="C21:P21" si="6">+C18-SUM(C19:C20)</f>
+        <f t="shared" ref="C21:Q21" si="6">+C18-SUM(C19:C20)</f>
         <v>34670</v>
       </c>
       <c r="D21" s="4">
@@ -3170,7 +3208,10 @@
         <f t="shared" si="6"/>
         <v>55295</v>
       </c>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="4">
+        <f t="shared" si="6"/>
+        <v>56058</v>
+      </c>
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4">
@@ -3204,7 +3245,7 @@
     </row>
     <row r="22" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="4">
         <v>6628</v>
@@ -3251,7 +3292,9 @@
       <c r="P22" s="4">
         <v>8504</v>
       </c>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="4">
+        <v>8915</v>
+      </c>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4">
@@ -3278,7 +3321,7 @@
     </row>
     <row r="23" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C23" s="4">
         <v>5126</v>
@@ -3325,7 +3368,9 @@
       <c r="P23" s="4">
         <v>6584</v>
       </c>
-      <c r="Q23" s="4"/>
+      <c r="Q23" s="4">
+        <v>6814</v>
+      </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4">
@@ -3352,7 +3397,7 @@
     </row>
     <row r="24" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C24" s="4">
         <v>1398</v>
@@ -3399,7 +3444,9 @@
       <c r="P24" s="4">
         <v>1932</v>
       </c>
-      <c r="Q24" s="4"/>
+      <c r="Q24" s="4">
+        <v>1931</v>
+      </c>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4">
@@ -3426,10 +3473,10 @@
     </row>
     <row r="25" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25" s="4">
-        <f t="shared" ref="C25:P25" si="9">+C21-SUM(C22:C24)</f>
+        <f t="shared" ref="C25:Q25" si="9">+C21-SUM(C22:C24)</f>
         <v>21518</v>
       </c>
       <c r="D25" s="4">
@@ -3484,7 +3531,10 @@
         <f t="shared" si="9"/>
         <v>38275</v>
       </c>
-      <c r="Q25" s="4"/>
+      <c r="Q25" s="4">
+        <f t="shared" si="9"/>
+        <v>38398</v>
+      </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4">
@@ -3518,7 +3568,7 @@
     </row>
     <row r="26" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="4">
         <v>54</v>
@@ -3565,7 +3615,9 @@
       <c r="P26" s="4">
         <v>9971</v>
       </c>
-      <c r="Q26" s="4"/>
+      <c r="Q26" s="4">
+        <v>942</v>
+      </c>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
       <c r="T26" s="4">
@@ -3592,10 +3644,10 @@
     </row>
     <row r="27" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="4">
-        <f t="shared" ref="C27:P27" si="12">C25+C26</f>
+        <f t="shared" ref="C27:Q27" si="12">C25+C26</f>
         <v>21572</v>
       </c>
       <c r="D27" s="4">
@@ -3650,7 +3702,10 @@
         <f t="shared" si="12"/>
         <v>48246</v>
       </c>
-      <c r="Q27" s="4"/>
+      <c r="Q27" s="4">
+        <f t="shared" si="12"/>
+        <v>39340</v>
+      </c>
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4">
@@ -3684,7 +3739,7 @@
     </row>
     <row r="28" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="4">
         <v>4016</v>
@@ -3731,7 +3786,9 @@
       <c r="P28" s="4">
         <v>9788</v>
       </c>
-      <c r="Q28" s="4"/>
+      <c r="Q28" s="4">
+        <v>7562</v>
+      </c>
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4">
@@ -3758,10 +3815,10 @@
     </row>
     <row r="29" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="4">
-        <f t="shared" ref="C29:P30" si="15">+C27-C28</f>
+        <f t="shared" ref="C29:Q29" si="15">+C27-C28</f>
         <v>17556</v>
       </c>
       <c r="D29" s="4">
@@ -3816,7 +3873,10 @@
         <f t="shared" si="15"/>
         <v>38458</v>
       </c>
-      <c r="Q29" s="4"/>
+      <c r="Q29" s="4">
+        <f t="shared" si="15"/>
+        <v>31778</v>
+      </c>
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4">
@@ -3875,10 +3935,10 @@
     </row>
     <row r="31" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="23">
-        <f t="shared" ref="C31:P31" si="18">C29/C32</f>
+        <f t="shared" ref="C31:Q31" si="18">C29/C32</f>
         <v>2.3542979750569932</v>
       </c>
       <c r="D31" s="23">
@@ -3933,7 +3993,10 @@
         <f t="shared" si="18"/>
         <v>5.1753465213295655</v>
       </c>
-      <c r="Q31" s="23"/>
+      <c r="Q31" s="23">
+        <f t="shared" si="18"/>
+        <v>4.2792889846485318</v>
+      </c>
       <c r="R31" s="23"/>
       <c r="S31" s="4"/>
       <c r="T31" s="23">
@@ -4014,7 +4077,9 @@
       <c r="P32" s="4">
         <v>7431</v>
       </c>
-      <c r="Q32" s="4"/>
+      <c r="Q32" s="4">
+        <v>7426</v>
+      </c>
       <c r="R32" s="4"/>
       <c r="S32" s="4"/>
       <c r="T32" s="4">
@@ -4066,7 +4131,7 @@
     </row>
     <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B34" s="34" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -4112,7 +4177,10 @@
         <f>+P14/L14-1</f>
         <v>0.28824772940808008</v>
       </c>
-      <c r="Q34" s="4"/>
+      <c r="Q34" s="24">
+        <f>+Q14/M14-1</f>
+        <v>0.29643751635452875</v>
+      </c>
       <c r="R34" s="4"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
@@ -4143,14 +4211,14 @@
     </row>
     <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="24">
-        <f t="shared" ref="G35:P37" si="22">G16/D16-1</f>
+        <f t="shared" ref="G35:Q37" si="22">G16/D16-1</f>
         <v>-5.9453895985953853E-2</v>
       </c>
       <c r="H35" s="24">
@@ -4189,7 +4257,10 @@
         <f t="shared" si="22"/>
         <v>7.3895162869638931E-2</v>
       </c>
-      <c r="Q35" s="24"/>
+      <c r="Q35" s="24">
+        <f t="shared" si="22"/>
+        <v>-0.11945611577964521</v>
+      </c>
       <c r="R35" s="24"/>
       <c r="S35" s="4"/>
       <c r="T35" s="24"/>
@@ -4220,7 +4291,7 @@
     </row>
     <row r="36" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -4266,7 +4337,10 @@
         <f t="shared" si="22"/>
         <v>0.1840283485853107</v>
       </c>
-      <c r="Q36" s="24"/>
+      <c r="Q36" s="24">
+        <f t="shared" si="22"/>
+        <v>0.14319197369530401</v>
+      </c>
       <c r="R36" s="24"/>
       <c r="S36" s="4"/>
       <c r="T36" s="24"/>
@@ -4297,7 +4371,7 @@
     </row>
     <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="22"/>
       <c r="D37" s="22"/>
@@ -4343,7 +4417,10 @@
         <f t="shared" si="22"/>
         <v>0.15994919076299485</v>
       </c>
-      <c r="Q37" s="25"/>
+      <c r="Q37" s="25">
+        <f t="shared" si="22"/>
+        <v>8.4313392027838496E-2</v>
+      </c>
       <c r="R37" s="25"/>
       <c r="S37" s="22"/>
       <c r="T37" s="25"/>
@@ -4374,7 +4451,7 @@
     </row>
     <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C38" s="24">
         <f t="shared" ref="C38:N38" si="24">(C16-C19)/C16</f>
@@ -4432,27 +4509,30 @@
         <f t="shared" si="25"/>
         <v>0.78694304297611084</v>
       </c>
-      <c r="Q38" s="24"/>
+      <c r="Q38" s="24">
+        <f t="shared" ref="Q38" si="26">(Q16-Q19)/Q16</f>
+        <v>0.81887467691695937</v>
+      </c>
       <c r="R38" s="24"/>
       <c r="S38" s="4"/>
       <c r="T38" s="24">
-        <f t="shared" ref="T38" si="26">(T16-T19)/T16</f>
+        <f t="shared" ref="T38" si="27">(T16-T19)/T16</f>
         <v>0.75369689264254036</v>
       </c>
       <c r="U38" s="24">
-        <f t="shared" ref="U38:X38" si="27">(U16-U19)/U16</f>
+        <f t="shared" ref="U38:X38" si="28">(U16-U19)/U16</f>
         <v>0.76459781602269217</v>
       </c>
       <c r="V38" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.74366153586402906</v>
       </c>
       <c r="W38" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.73788703734257277</v>
       </c>
       <c r="X38" s="24">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0.72481800336944935</v>
       </c>
       <c r="Y38" s="24">
@@ -4466,85 +4546,88 @@
     </row>
     <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C39" s="24">
-        <f t="shared" ref="C39:N39" si="28">(C17-C20)/C17</f>
+        <f t="shared" ref="C39:N39" si="29">(C17-C20)/C17</f>
         <v>0.67569296995433525</v>
       </c>
       <c r="D39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.67435826662986476</v>
       </c>
       <c r="E39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.67299900721779493</v>
       </c>
       <c r="F39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.67144600366076879</v>
       </c>
       <c r="G39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.68837538431506518</v>
       </c>
       <c r="H39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.68293135866663568</v>
       </c>
       <c r="I39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.68363928714993971</v>
       </c>
       <c r="J39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.64577751892836344</v>
       </c>
       <c r="K39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.66599089698487468</v>
       </c>
       <c r="L39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.66407054462396797</v>
       </c>
       <c r="M39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.65510438928160453</v>
       </c>
       <c r="N39" s="24">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.65095691762920493</v>
       </c>
       <c r="O39" s="24">
-        <f t="shared" ref="O39:P39" si="29">(O17-O20)/O17</f>
+        <f t="shared" ref="O39:P39" si="30">(O17-O20)/O17</f>
         <v>0.65796505319751908</v>
       </c>
       <c r="P39" s="24">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.65331214711054886</v>
       </c>
-      <c r="Q39" s="24"/>
+      <c r="Q39" s="24">
+        <f t="shared" ref="Q39" si="31">(Q17-Q20)/Q17</f>
+        <v>0.64460079354543709</v>
+      </c>
       <c r="R39" s="24"/>
       <c r="S39" s="4"/>
       <c r="T39" s="24">
-        <f t="shared" ref="T39" si="30">(T17-T20)/T17</f>
+        <f t="shared" ref="T39" si="32">(T17-T20)/T17</f>
         <v>0.55437146585471941</v>
       </c>
       <c r="U39" s="24">
-        <f t="shared" ref="U39:X39" si="31">(U17-U20)/U17</f>
+        <f t="shared" ref="U39:X39" si="33">(U17-U20)/U17</f>
         <v>0.59904766985888447</v>
       </c>
       <c r="V39" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.64940111736450412</v>
       </c>
       <c r="W39" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.65280632159186858</v>
       </c>
       <c r="X39" s="24">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.67354771220519505</v>
       </c>
       <c r="Y39" s="24">
@@ -4558,85 +4641,88 @@
     </row>
     <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40" s="24">
-        <f t="shared" ref="C40:N40" si="32">C21/C18</f>
+        <f t="shared" ref="C40:N40" si="34">C21/C18</f>
         <v>0.69171222217788597</v>
       </c>
       <c r="D40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.66845507801391546</v>
       </c>
       <c r="E40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.69487485101311086</v>
       </c>
       <c r="F40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.70109807969531401</v>
       </c>
       <c r="G40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.71155581506449384</v>
       </c>
       <c r="H40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.68360206385037081</v>
       </c>
       <c r="I40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.70084710142584628</v>
       </c>
       <c r="J40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.69589197707293715</v>
       </c>
       <c r="K40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.69354273080734929</v>
       </c>
       <c r="L40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.68693991268382348</v>
       </c>
       <c r="M40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.6871663859789342</v>
       </c>
       <c r="N40" s="24">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.68584921704320978</v>
       </c>
       <c r="O40" s="24">
-        <f t="shared" ref="O40:P40" si="33">O21/O18</f>
+        <f t="shared" ref="O40:P40" si="35">O21/O18</f>
         <v>0.69045871795862135</v>
       </c>
       <c r="P40" s="24">
-        <f t="shared" si="33"/>
+        <f t="shared" si="35"/>
         <v>0.68036125158416694</v>
       </c>
-      <c r="Q40" s="24"/>
+      <c r="Q40" s="24">
+        <f t="shared" ref="Q40" si="36">Q21/Q18</f>
+        <v>0.67632652076345823</v>
+      </c>
       <c r="R40" s="24"/>
       <c r="S40" s="4"/>
       <c r="T40" s="24">
-        <f t="shared" ref="T40" si="34">T21/T18</f>
+        <f t="shared" ref="T40" si="37">T21/T18</f>
         <v>0.65901957200638894</v>
       </c>
       <c r="U40" s="24">
-        <f t="shared" ref="U40:X40" si="35">U21/U18</f>
+        <f t="shared" ref="U40:X40" si="38">U21/U18</f>
         <v>0.67781001992797962</v>
       </c>
       <c r="V40" s="24">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.68925800771024703</v>
       </c>
       <c r="W40" s="24">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.68401674484289099</v>
       </c>
       <c r="X40" s="24">
-        <f t="shared" si="35"/>
+        <f t="shared" si="38"/>
         <v>0.68920085883491022</v>
       </c>
       <c r="Y40" s="24">
@@ -4650,85 +4736,88 @@
     </row>
     <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41" s="24">
-        <f t="shared" ref="C41:N41" si="36">C25/C18</f>
+        <f t="shared" ref="C41:N41" si="39">C25/C18</f>
         <v>0.42931247755476637</v>
       </c>
       <c r="D41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.3867328947617874</v>
       </c>
       <c r="E41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.42287681858599618</v>
       </c>
       <c r="F41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.4316503230169606</v>
       </c>
       <c r="G41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.47587451563246458</v>
       </c>
       <c r="H41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.43585940019348596</v>
       </c>
       <c r="I41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.44587603866921011</v>
       </c>
       <c r="J41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.43142737960974553</v>
       </c>
       <c r="K41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.46583822520393381</v>
       </c>
       <c r="L41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.45457548253676472</v>
       </c>
       <c r="M41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.45671224274255701</v>
       </c>
       <c r="N41" s="24">
-        <f t="shared" si="36"/>
+        <f t="shared" si="39"/>
         <v>0.44901296424693554</v>
       </c>
       <c r="O41" s="24">
-        <f t="shared" ref="O41:P41" si="37">O25/O18</f>
+        <f t="shared" ref="O41:P41" si="40">O25/O18</f>
         <v>0.48872838695557014</v>
       </c>
       <c r="P41" s="24">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>0.47094360980891564</v>
       </c>
-      <c r="Q41" s="24"/>
+      <c r="Q41" s="24">
+        <f t="shared" ref="Q41" si="41">Q25/Q18</f>
+        <v>0.46326279468185216</v>
+      </c>
       <c r="R41" s="24"/>
       <c r="S41" s="4"/>
       <c r="T41" s="24">
-        <f t="shared" ref="T41" si="38">T25/T18</f>
+        <f t="shared" ref="T41" si="42">T25/T18</f>
         <v>0.3413698020549415</v>
       </c>
       <c r="U41" s="24">
-        <f t="shared" ref="U41:X41" si="39">U25/U18</f>
+        <f t="shared" ref="U41:X41" si="43">U25/U18</f>
         <v>0.37030381428521486</v>
       </c>
       <c r="V41" s="24">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>0.41594878872971303</v>
       </c>
       <c r="W41" s="24">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>0.4205527815604983</v>
       </c>
       <c r="X41" s="24">
-        <f t="shared" si="39"/>
+        <f t="shared" si="43"/>
         <v>0.41772880636104098</v>
       </c>
       <c r="Y41" s="24">
@@ -4742,85 +4831,88 @@
     </row>
     <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42" s="24">
-        <f t="shared" ref="C42:N42" si="40">C28/C27</f>
+        <f t="shared" ref="C42:N42" si="44">C28/C27</f>
         <v>0.18616725384758021</v>
       </c>
       <c r="D42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.19243817296818919</v>
       </c>
       <c r="E42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.19291668504388479</v>
       </c>
       <c r="F42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.18789177821814212</v>
       </c>
       <c r="G42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.18303767775985927</v>
       </c>
       <c r="H42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.17552589911784663</v>
       </c>
       <c r="I42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.17914468514984846</v>
       </c>
       <c r="J42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.19130275229357799</v>
       </c>
       <c r="K42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.18507383791998414</v>
       </c>
       <c r="L42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.17902264600715137</v>
       </c>
       <c r="M42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.17697676642126398</v>
       </c>
       <c r="N42" s="24">
-        <f t="shared" si="40"/>
+        <f t="shared" si="44"/>
         <v>0.16504169732646554</v>
       </c>
       <c r="O42" s="24">
-        <f t="shared" ref="O42:P42" si="41">O28/O27</f>
+        <f t="shared" ref="O42:P42" si="45">O28/O27</f>
         <v>0.19107314655549401</v>
       </c>
       <c r="P42" s="24">
-        <f t="shared" si="41"/>
+        <f t="shared" si="45"/>
         <v>0.20287692243916594</v>
       </c>
-      <c r="Q42" s="24"/>
+      <c r="Q42" s="24">
+        <f t="shared" ref="Q42" si="46">Q28/Q27</f>
+        <v>0.19222165734621249</v>
+      </c>
       <c r="R42" s="24"/>
       <c r="S42" s="4"/>
       <c r="T42" s="24">
-        <f t="shared" ref="T42" si="42">T28/T27</f>
+        <f t="shared" ref="T42" si="47">T28/T27</f>
         <v>0.10181285478850027</v>
       </c>
       <c r="U42" s="24">
-        <f t="shared" ref="U42:X42" si="43">U28/U27</f>
+        <f t="shared" ref="U42:X42" si="48">U28/U27</f>
         <v>0.16507655177615205</v>
       </c>
       <c r="V42" s="24">
-        <f t="shared" si="43"/>
+        <f t="shared" si="48"/>
         <v>0.13826615285083402</v>
       </c>
       <c r="W42" s="24">
-        <f t="shared" si="43"/>
+        <f t="shared" si="48"/>
         <v>0.13113383343685794</v>
       </c>
       <c r="X42" s="24">
-        <f t="shared" si="43"/>
+        <f t="shared" si="48"/>
         <v>0.18978625253328257</v>
       </c>
       <c r="Y42" s="24">
@@ -4859,7 +4951,7 @@
     </row>
     <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -4902,7 +4994,7 @@
     </row>
     <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -4945,7 +5037,7 @@
     </row>
     <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -4988,7 +5080,7 @@
     </row>
     <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -5031,7 +5123,7 @@
     </row>
     <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -5074,7 +5166,7 @@
     </row>
     <row r="49" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
@@ -5094,19 +5186,19 @@
       <c r="R49" s="4"/>
       <c r="S49" s="4"/>
       <c r="T49" s="4">
-        <f t="shared" ref="T49:W49" si="44">+SUM(T44:T48)</f>
+        <f t="shared" ref="T49:W49" si="49">+SUM(T44:T48)</f>
         <v>175552</v>
       </c>
       <c r="U49" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>181915</v>
       </c>
       <c r="V49" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>184406</v>
       </c>
       <c r="W49" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="49"/>
         <v>169684</v>
       </c>
       <c r="X49" s="4">
@@ -5124,7 +5216,7 @@
     </row>
     <row r="50" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
@@ -5167,7 +5259,7 @@
     </row>
     <row r="51" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
@@ -5210,7 +5302,7 @@
     </row>
     <row r="52" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
@@ -5253,7 +5345,7 @@
     </row>
     <row r="53" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
@@ -5296,7 +5388,7 @@
     </row>
     <row r="54" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
@@ -5339,7 +5431,7 @@
     </row>
     <row r="55" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B55" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
@@ -5382,7 +5474,7 @@
     </row>
     <row r="56" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
@@ -5402,23 +5494,23 @@
       <c r="R56" s="4"/>
       <c r="S56" s="4"/>
       <c r="T56" s="4">
-        <f t="shared" ref="T56:X56" si="45">+SUM(T50:T55)</f>
+        <f t="shared" ref="T56:X56" si="50">+SUM(T50:T55)</f>
         <v>111004</v>
       </c>
       <c r="U56" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="50"/>
         <v>119396</v>
       </c>
       <c r="V56" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="50"/>
         <v>149373</v>
       </c>
       <c r="W56" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="50"/>
         <v>195156</v>
       </c>
       <c r="X56" s="4">
-        <f t="shared" si="45"/>
+        <f t="shared" si="50"/>
         <v>227719</v>
       </c>
       <c r="Y56" s="4">
@@ -5432,7 +5524,7 @@
     </row>
     <row r="57" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B57" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C57" s="22"/>
       <c r="D57" s="22"/>
@@ -5452,31 +5544,31 @@
       <c r="R57" s="22"/>
       <c r="S57" s="22"/>
       <c r="T57" s="22">
-        <f t="shared" ref="T57:Z57" si="46">+T49+T56</f>
+        <f t="shared" ref="T57:Z57" si="51">+T49+T56</f>
         <v>286556</v>
       </c>
       <c r="U57" s="22">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>301311</v>
       </c>
       <c r="V57" s="22">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>333779</v>
       </c>
       <c r="W57" s="22">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>364840</v>
       </c>
       <c r="X57" s="22">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>411976</v>
       </c>
       <c r="Y57" s="22">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>512163</v>
       </c>
       <c r="Z57" s="22">
-        <f t="shared" si="46"/>
+        <f t="shared" si="51"/>
         <v>619003</v>
       </c>
     </row>
@@ -5507,7 +5599,7 @@
     </row>
     <row r="59" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
@@ -5550,7 +5642,7 @@
     </row>
     <row r="60" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
@@ -5593,7 +5685,7 @@
     </row>
     <row r="61" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
@@ -5636,7 +5728,7 @@
     </row>
     <row r="62" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
@@ -5679,7 +5771,7 @@
     </row>
     <row r="63" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
@@ -5722,7 +5814,7 @@
     </row>
     <row r="64" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
@@ -5765,7 +5857,7 @@
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
@@ -5808,7 +5900,7 @@
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
@@ -5828,23 +5920,23 @@
       <c r="R66" s="4"/>
       <c r="S66" s="4"/>
       <c r="T66" s="4">
-        <f t="shared" ref="T66:X66" si="47">+SUM(T59:T65)</f>
+        <f t="shared" ref="T66:X66" si="52">+SUM(T59:T65)</f>
         <v>69420</v>
       </c>
       <c r="U66" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>72310</v>
       </c>
       <c r="V66" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>88657</v>
       </c>
       <c r="W66" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>95082</v>
       </c>
       <c r="X66" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" si="52"/>
         <v>104149</v>
       </c>
       <c r="Y66" s="4">
@@ -5901,7 +5993,7 @@
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
@@ -5944,7 +6036,7 @@
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B69" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
@@ -5987,7 +6079,7 @@
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
@@ -6030,7 +6122,7 @@
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
@@ -6073,7 +6165,7 @@
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -6116,7 +6208,7 @@
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -6136,23 +6228,23 @@
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
       <c r="T73" s="4">
-        <f t="shared" ref="T73:X73" si="48">+SUM(T67:T72)</f>
+        <f t="shared" ref="T73:X73" si="53">+SUM(T67:T72)</f>
         <v>114806</v>
       </c>
       <c r="U73" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
         <v>110697</v>
       </c>
       <c r="V73" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
         <v>103107</v>
       </c>
       <c r="W73" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
         <v>103216</v>
       </c>
       <c r="X73" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="53"/>
         <v>101604</v>
       </c>
       <c r="Y73" s="4">
@@ -6166,7 +6258,7 @@
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
@@ -6186,23 +6278,23 @@
       <c r="R74" s="4"/>
       <c r="S74" s="4"/>
       <c r="T74" s="22">
-        <f t="shared" ref="T74:X74" si="49">+T73+T66</f>
+        <f t="shared" ref="T74:X74" si="54">+T73+T66</f>
         <v>184226</v>
       </c>
       <c r="U74" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>183007</v>
       </c>
       <c r="V74" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>191764</v>
       </c>
       <c r="W74" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>198298</v>
       </c>
       <c r="X74" s="22">
-        <f t="shared" si="49"/>
+        <f t="shared" si="54"/>
         <v>205753</v>
       </c>
       <c r="Y74" s="22">
@@ -6216,7 +6308,7 @@
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
@@ -6259,7 +6351,7 @@
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
@@ -6279,19 +6371,19 @@
       <c r="R76" s="4"/>
       <c r="S76" s="4"/>
       <c r="T76" s="22">
-        <f t="shared" ref="T76:W76" si="50">+T74+T75</f>
+        <f t="shared" ref="T76:W76" si="55">+T74+T75</f>
         <v>286556</v>
       </c>
       <c r="U76" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" si="55"/>
         <v>301311</v>
       </c>
       <c r="V76" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" si="55"/>
         <v>333752</v>
       </c>
       <c r="W76" s="22">
-        <f t="shared" si="50"/>
+        <f t="shared" si="55"/>
         <v>364840</v>
       </c>
       <c r="X76" s="22">
@@ -6334,10 +6426,10 @@
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A78" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
@@ -6365,7 +6457,7 @@
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
@@ -6385,37 +6477,37 @@
       <c r="R79" s="4"/>
       <c r="S79" s="4"/>
       <c r="T79" s="4">
-        <f t="shared" ref="T79:Z79" si="51">T29</f>
+        <f t="shared" ref="T79:Z79" si="56">T29</f>
         <v>39240</v>
       </c>
       <c r="U79" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>44281</v>
       </c>
       <c r="V79" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>61271</v>
       </c>
       <c r="W79" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>72738</v>
       </c>
       <c r="X79" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>72361</v>
       </c>
       <c r="Y79" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>88136</v>
       </c>
       <c r="Z79" s="4">
-        <f t="shared" si="51"/>
+        <f t="shared" si="56"/>
         <v>101832</v>
       </c>
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
@@ -6458,7 +6550,7 @@
     </row>
     <row r="81" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
@@ -6501,7 +6593,7 @@
     </row>
     <row r="82" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
@@ -6544,7 +6636,7 @@
     </row>
     <row r="83" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B83" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
@@ -6587,7 +6679,7 @@
     </row>
     <row r="84" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B84" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
@@ -6615,7 +6707,7 @@
     </row>
     <row r="85" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B85" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
@@ -6658,7 +6750,7 @@
     </row>
     <row r="86" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B86" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
@@ -6701,7 +6793,7 @@
     </row>
     <row r="87" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B87" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
@@ -6744,7 +6836,7 @@
     </row>
     <row r="88" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B88" s="26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
@@ -6787,7 +6879,7 @@
     </row>
     <row r="89" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B89" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
@@ -6830,7 +6922,7 @@
     </row>
     <row r="90" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B90" s="26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
@@ -6873,7 +6965,7 @@
     </row>
     <row r="91" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B91" s="26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
@@ -6916,7 +7008,7 @@
     </row>
     <row r="92" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B92" s="26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
@@ -6959,7 +7051,7 @@
     </row>
     <row r="93" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B93" s="26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
@@ -7002,7 +7094,7 @@
     </row>
     <row r="94" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B94" s="27" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
@@ -7022,23 +7114,23 @@
       <c r="R94" s="4"/>
       <c r="S94" s="4"/>
       <c r="T94" s="4">
-        <f t="shared" ref="T94:X94" si="52">+SUM(T85:T93)</f>
+        <f t="shared" ref="T94:X94" si="57">+SUM(T85:T93)</f>
         <v>3866</v>
       </c>
       <c r="U94" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="57"/>
         <v>-1483</v>
       </c>
       <c r="V94" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="57"/>
         <v>-936</v>
       </c>
       <c r="W94" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="57"/>
         <v>446</v>
       </c>
       <c r="X94" s="4">
-        <f t="shared" si="52"/>
+        <f t="shared" si="57"/>
         <v>-2388</v>
       </c>
       <c r="Y94" s="4">
@@ -7052,7 +7144,7 @@
     </row>
     <row r="95" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B95" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
@@ -7064,31 +7156,35 @@
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
+      <c r="M95" s="22">
+        <v>37044</v>
+      </c>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
       <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
+      <c r="Q95" s="22">
+        <v>46679</v>
+      </c>
       <c r="R95" s="4"/>
       <c r="S95" s="4"/>
       <c r="T95" s="22">
-        <f t="shared" ref="T95:X95" si="53">+T79+SUM(T80:T83,T94)</f>
+        <f t="shared" ref="T95:X95" si="58">+T79+SUM(T80:T83,T94)</f>
         <v>52185</v>
       </c>
       <c r="U95" s="22">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>60675</v>
       </c>
       <c r="V95" s="22">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>76740</v>
       </c>
       <c r="W95" s="22">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>89035</v>
       </c>
       <c r="X95" s="22">
-        <f t="shared" si="53"/>
+        <f t="shared" si="58"/>
         <v>87582</v>
       </c>
       <c r="Y95" s="22">
@@ -7102,7 +7198,7 @@
     </row>
     <row r="96" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B96" s="27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
@@ -7145,7 +7241,7 @@
     </row>
     <row r="97" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B97" s="27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -7188,7 +7284,7 @@
     </row>
     <row r="98" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B98" s="27" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
@@ -7231,7 +7327,7 @@
     </row>
     <row r="99" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B99" s="27" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
@@ -7274,7 +7370,7 @@
     </row>
     <row r="100" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B100" s="27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
@@ -7317,7 +7413,7 @@
     </row>
     <row r="101" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B101" s="27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
@@ -7360,7 +7456,7 @@
     </row>
     <row r="102" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B102" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
@@ -7405,7 +7501,7 @@
     </row>
     <row r="103" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B103" s="28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
@@ -7425,23 +7521,23 @@
       <c r="R103" s="4"/>
       <c r="S103" s="4"/>
       <c r="T103" s="22">
-        <f t="shared" ref="T103:X103" si="54">+SUM(T96:T102)</f>
+        <f t="shared" ref="T103:X103" si="59">+SUM(T96:T102)</f>
         <v>-36887</v>
       </c>
       <c r="U103" s="22">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>-46031</v>
       </c>
       <c r="V103" s="22">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>-48486</v>
       </c>
       <c r="W103" s="22">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>-58876</v>
       </c>
       <c r="X103" s="22">
-        <f t="shared" si="54"/>
+        <f t="shared" si="59"/>
         <v>-43935</v>
       </c>
       <c r="Y103" s="22">
@@ -7455,7 +7551,7 @@
     </row>
     <row r="104" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B104" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
@@ -7467,11 +7563,15 @@
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
+      <c r="M104" s="4">
+        <v>-16745</v>
+      </c>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
       <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
+      <c r="Q104" s="4">
+        <v>-30876</v>
+      </c>
       <c r="R104" s="4"/>
       <c r="S104" s="4"/>
       <c r="T104" s="4">
@@ -7498,7 +7598,7 @@
     </row>
     <row r="105" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B105" s="27" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
@@ -7541,7 +7641,7 @@
     </row>
     <row r="106" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B106" s="27" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
@@ -7584,7 +7684,7 @@
     </row>
     <row r="107" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B107" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
@@ -7627,7 +7727,7 @@
     </row>
     <row r="108" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B108" s="27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
@@ -7670,7 +7770,7 @@
     </row>
     <row r="109" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B109" s="27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -7713,7 +7813,7 @@
     </row>
     <row r="110" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B110" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
@@ -7733,23 +7833,23 @@
       <c r="R110" s="4"/>
       <c r="S110" s="4"/>
       <c r="T110" s="22">
-        <f t="shared" ref="T110:X110" si="55">+SUM(T104:T109)</f>
+        <f t="shared" ref="T110:X110" si="60">+SUM(T104:T109)</f>
         <v>-15773</v>
       </c>
       <c r="U110" s="22">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-12223</v>
       </c>
       <c r="V110" s="22">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-27577</v>
       </c>
       <c r="W110" s="22">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-30311</v>
       </c>
       <c r="X110" s="22">
-        <f t="shared" si="55"/>
+        <f t="shared" si="60"/>
         <v>-16358</v>
       </c>
       <c r="Y110" s="22">
@@ -7763,7 +7863,7 @@
     </row>
     <row r="111" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B111" s="27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
@@ -7800,7 +7900,7 @@
     </row>
     <row r="112" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B112" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
@@ -7820,23 +7920,23 @@
       <c r="R112" s="4"/>
       <c r="S112" s="4"/>
       <c r="T112" s="22">
-        <f t="shared" ref="T112:X112" si="56">+T111+T110+T103+T95</f>
+        <f t="shared" ref="T112:X112" si="61">+T111+T110+T103+T95</f>
         <v>-475</v>
       </c>
       <c r="U112" s="22">
-        <f t="shared" si="56"/>
+        <f t="shared" si="61"/>
         <v>2421</v>
       </c>
       <c r="V112" s="22">
-        <f t="shared" si="56"/>
+        <f t="shared" si="61"/>
         <v>677</v>
       </c>
       <c r="W112" s="22">
-        <f t="shared" si="56"/>
+        <f t="shared" si="61"/>
         <v>-293</v>
       </c>
       <c r="X112" s="22">
-        <f t="shared" si="56"/>
+        <f t="shared" si="61"/>
         <v>27095</v>
       </c>
       <c r="Y112" s="22">
@@ -7850,7 +7950,7 @@
     </row>
     <row r="113" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B113" s="27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
@@ -7898,7 +7998,7 @@
     </row>
     <row r="114" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B114" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
@@ -7972,7 +8072,7 @@
     </row>
     <row r="116" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B116" s="28" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C116" s="22"/>
       <c r="D116" s="22"/>
@@ -7992,31 +8092,31 @@
       <c r="R116" s="22"/>
       <c r="S116" s="22"/>
       <c r="T116" s="22">
-        <f t="shared" ref="T116:Z116" si="57">T25+T80+T94+T104</f>
+        <f t="shared" ref="T116:Z116" si="62">T25+T80+T94+T104</f>
         <v>44582</v>
       </c>
       <c r="U116" s="22">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>48831</v>
       </c>
       <c r="V116" s="22">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>60044</v>
       </c>
       <c r="W116" s="22">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>74403</v>
       </c>
       <c r="X116" s="22">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>71979</v>
       </c>
       <c r="Y116" s="22">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>89067</v>
       </c>
       <c r="Z116" s="22">
-        <f t="shared" si="57"/>
+        <f t="shared" si="62"/>
         <v>92780</v>
       </c>
     </row>
@@ -20741,46 +20841,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B2" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="J2" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B3" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" s="29"/>
       <c r="E4" s="29"/>
@@ -20794,12 +20894,12 @@
       <c r="K4" s="30"/>
       <c r="L4" s="30"/>
       <c r="N4" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D5" s="24"/>
       <c r="E5" s="24"/>
@@ -20810,12 +20910,12 @@
       <c r="K5" s="31"/>
       <c r="L5" s="31"/>
       <c r="N5" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D6" s="24"/>
       <c r="E6" s="24"/>
@@ -20826,12 +20926,12 @@
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
       <c r="N6" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D7" s="24"/>
       <c r="E7" s="24"/>
@@ -20842,12 +20942,12 @@
       <c r="K7" s="31"/>
       <c r="L7" s="31"/>
       <c r="N7" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8" s="24"/>
       <c r="E8" s="24"/>
@@ -20861,12 +20961,12 @@
       <c r="K8" s="31"/>
       <c r="L8" s="31"/>
       <c r="N8" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D9" s="31"/>
       <c r="E9" s="31"/>
@@ -20880,12 +20980,12 @@
       <c r="K9" s="31"/>
       <c r="L9" s="31"/>
       <c r="N9" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D10" s="24"/>
       <c r="E10" s="24"/>
@@ -20896,12 +20996,12 @@
       <c r="K10" s="31"/>
       <c r="L10" s="31"/>
       <c r="N10" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D11" s="31"/>
       <c r="E11" s="31"/>
@@ -20912,17 +21012,17 @@
       <c r="K11" s="31"/>
       <c r="L11" s="31"/>
       <c r="N11" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B14" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
@@ -20933,12 +21033,12 @@
       <c r="K15" s="31"/>
       <c r="L15" s="31"/>
       <c r="N15" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
@@ -20949,12 +21049,12 @@
       <c r="K16" s="31"/>
       <c r="L16" s="31"/>
       <c r="N16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -20965,12 +21065,12 @@
       <c r="K17" s="31"/>
       <c r="L17" s="31"/>
       <c r="N17" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
@@ -20981,12 +21081,12 @@
       <c r="K18" s="31"/>
       <c r="L18" s="31"/>
       <c r="N18" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
@@ -20997,17 +21097,17 @@
       <c r="K19" s="31"/>
       <c r="L19" s="31"/>
       <c r="N19" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D22" s="30"/>
       <c r="E22" s="30"/>
@@ -21018,12 +21118,12 @@
       <c r="K22" s="30"/>
       <c r="L22" s="30"/>
       <c r="N22" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D23" s="30"/>
       <c r="E23" s="30"/>
@@ -21034,12 +21134,12 @@
       <c r="K23" s="30"/>
       <c r="L23" s="30"/>
       <c r="N23" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D24" s="24"/>
       <c r="E24" s="24"/>
@@ -21050,12 +21150,12 @@
       <c r="K24" s="31"/>
       <c r="L24" s="31"/>
       <c r="N24" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
@@ -21066,12 +21166,12 @@
       <c r="K25" s="31"/>
       <c r="L25" s="31"/>
       <c r="N25" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D26" s="24"/>
       <c r="E26" s="24"/>
@@ -21082,12 +21182,12 @@
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
       <c r="N26" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D27" s="24"/>
       <c r="E27" s="24"/>
@@ -21098,12 +21198,12 @@
       <c r="K27" s="31"/>
       <c r="L27" s="31"/>
       <c r="N27" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D28" s="30"/>
       <c r="E28" s="30"/>
@@ -21114,12 +21214,12 @@
       <c r="K28" s="30"/>
       <c r="L28" s="30"/>
       <c r="N28" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D29" s="30"/>
       <c r="E29" s="30"/>
@@ -21130,12 +21230,12 @@
       <c r="K29" s="30"/>
       <c r="L29" s="30"/>
       <c r="N29" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D30" s="30"/>
       <c r="E30" s="30"/>
@@ -21146,12 +21246,12 @@
       <c r="K30" s="30"/>
       <c r="L30" s="30"/>
       <c r="N30" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.2">
@@ -21166,7 +21266,7 @@
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D35" s="29"/>
       <c r="E35" s="29"/>
@@ -21177,7 +21277,7 @@
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D36" s="29"/>
       <c r="E36" s="29"/>
@@ -21207,7 +21307,7 @@
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B39" s="21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D39" s="29"/>
       <c r="E39" s="29"/>
@@ -21218,7 +21318,7 @@
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D40" s="30"/>
       <c r="E40" s="30"/>
@@ -21229,12 +21329,12 @@
       <c r="K40" s="30"/>
       <c r="L40" s="30"/>
       <c r="N40" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D41" s="32"/>
       <c r="E41" s="30"/>
@@ -21245,12 +21345,12 @@
       <c r="K41" s="30"/>
       <c r="L41" s="30"/>
       <c r="N41" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D42" s="30"/>
       <c r="E42" s="30"/>
@@ -21261,19 +21361,19 @@
       <c r="K42" s="30"/>
       <c r="L42" s="30"/>
       <c r="N42" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B43" s="21" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="K43" s="30"/>
       <c r="L43" s="30"/>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D44" s="30"/>
       <c r="E44" s="30"/>
@@ -21284,12 +21384,12 @@
       <c r="K44" s="30"/>
       <c r="L44" s="30"/>
       <c r="N44" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D45" s="30"/>
       <c r="E45" s="30"/>
@@ -21300,12 +21400,12 @@
       <c r="K45" s="30"/>
       <c r="L45" s="30"/>
       <c r="N45" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D46" s="30"/>
       <c r="E46" s="30"/>
@@ -21316,12 +21416,12 @@
       <c r="K46" s="30"/>
       <c r="L46" s="30"/>
       <c r="N46" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D47" s="30"/>
       <c r="E47" s="30"/>
@@ -21332,7 +21432,7 @@
       <c r="K47" s="30"/>
       <c r="L47" s="30"/>
       <c r="N47" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
